--- a/DataTables/Datas/#Aircraft.xlsx
+++ b/DataTables/Datas/#Aircraft.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="34">
   <si>
     <t>##var</t>
   </si>
@@ -25,10 +25,28 @@
     <t>thrusterId</t>
   </si>
   <si>
-    <t>weaponId</t>
-  </si>
-  <si>
-    <t>armorId</t>
+    <t>maxHp</t>
+  </si>
+  <si>
+    <t>defense</t>
+  </si>
+  <si>
+    <t>attack</t>
+  </si>
+  <si>
+    <t>interval</t>
+  </si>
+  <si>
+    <t>speed</t>
+  </si>
+  <si>
+    <t>bulletId</t>
+  </si>
+  <si>
+    <t>bulletSpeed</t>
+  </si>
+  <si>
+    <t>bulletSoundId</t>
   </si>
   <si>
     <t>deadEffId</t>
@@ -43,6 +61,9 @@
     <t>int</t>
   </si>
   <si>
+    <t>float</t>
+  </si>
+  <si>
     <t>##group</t>
   </si>
   <si>
@@ -58,10 +79,28 @@
     <t>推进器id</t>
   </si>
   <si>
-    <t>武器id</t>
-  </si>
-  <si>
-    <t>装甲id</t>
+    <t>最大生命值</t>
+  </si>
+  <si>
+    <t>防御力</t>
+  </si>
+  <si>
+    <t>攻击力</t>
+  </si>
+  <si>
+    <t>攻击间隔</t>
+  </si>
+  <si>
+    <t>移动速度</t>
+  </si>
+  <si>
+    <t>子弹id</t>
+  </si>
+  <si>
+    <t>子弹速度</t>
+  </si>
+  <si>
+    <t>子弹声音编号</t>
   </si>
   <si>
     <t>死亡特效id</t>
@@ -1039,18 +1078,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="5" outlineLevelCol="7"/>
+  <dimension ref="A1:N6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="5"/>
   <cols>
     <col min="1" max="1" width="8.21428571428571" customWidth="1"/>
-    <col min="2" max="2" width="7.14285714285714" customWidth="1"/>
-    <col min="3" max="3" width="11.3571428571429" customWidth="1"/>
-    <col min="4" max="4" width="11.7142857142857" customWidth="1"/>
-    <col min="5" max="7" width="22.9285714285714" customWidth="1"/>
-    <col min="8" max="8" width="9.57142857142857" customWidth="1"/>
+    <col min="2" max="2" width="11.3125" customWidth="1"/>
+    <col min="3" max="4" width="11.3571428571429" customWidth="1"/>
+    <col min="5" max="5" width="11.7142857142857" customWidth="1"/>
+    <col min="6" max="6" width="11.3571428571429" customWidth="1"/>
+    <col min="7" max="8" width="11.7142857142857" customWidth="1"/>
+    <col min="9" max="13" width="22.9285714285714" customWidth="1"/>
+    <col min="14" max="14" width="9.57142857142857" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:13">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1072,80 +1113,152 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:13">
       <c r="A2" s="1" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>10</v>
+        <v>17</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:14">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="B4" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="C4" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="D4" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="E4" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="F4" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="G4" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="H4" t="s">
-        <v>18</v>
+        <v>25</v>
+      </c>
+      <c r="I4" t="s">
+        <v>26</v>
+      </c>
+      <c r="J4" t="s">
+        <v>27</v>
+      </c>
+      <c r="K4" t="s">
+        <v>28</v>
+      </c>
+      <c r="L4" t="s">
+        <v>29</v>
+      </c>
+      <c r="M4" t="s">
+        <v>30</v>
+      </c>
+      <c r="N4" t="s">
+        <v>31</v>
       </c>
     </row>
-    <row r="5" spans="2:8">
+    <row r="5" spans="2:14">
       <c r="B5">
         <v>10000</v>
       </c>
@@ -1153,22 +1266,40 @@
         <v>20000</v>
       </c>
       <c r="D5">
-        <v>30000</v>
+        <v>1000</v>
       </c>
       <c r="E5">
-        <v>40000</v>
+        <v>100</v>
       </c>
       <c r="F5">
+        <v>110</v>
+      </c>
+      <c r="G5">
+        <v>0.2</v>
+      </c>
+      <c r="H5">
+        <v>20</v>
+      </c>
+      <c r="I5">
+        <v>50000</v>
+      </c>
+      <c r="J5">
+        <v>20</v>
+      </c>
+      <c r="K5">
+        <v>0</v>
+      </c>
+      <c r="L5">
         <v>70000</v>
       </c>
-      <c r="G5">
+      <c r="M5">
         <v>0</v>
       </c>
-      <c r="H5" t="s">
-        <v>19</v>
+      <c r="N5" t="s">
+        <v>32</v>
       </c>
     </row>
-    <row r="6" spans="2:8">
+    <row r="6" spans="2:14">
       <c r="B6">
         <v>10001</v>
       </c>
@@ -1176,19 +1307,37 @@
         <v>20001</v>
       </c>
       <c r="D6">
-        <v>30001</v>
+        <v>1000</v>
       </c>
       <c r="E6">
-        <v>40001</v>
+        <v>100</v>
       </c>
       <c r="F6">
+        <v>10</v>
+      </c>
+      <c r="G6">
+        <v>0.2</v>
+      </c>
+      <c r="H6">
+        <v>20</v>
+      </c>
+      <c r="I6">
+        <v>50000</v>
+      </c>
+      <c r="J6">
+        <v>20</v>
+      </c>
+      <c r="K6">
+        <v>0</v>
+      </c>
+      <c r="L6">
         <v>70001</v>
       </c>
-      <c r="G6">
+      <c r="M6">
         <v>1</v>
       </c>
-      <c r="H6" t="s">
-        <v>20</v>
+      <c r="N6" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>
